--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -9,12 +9,12 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="6420"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -24,12 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="25">
   <si>
     <t>Ano de Exercício</t>
   </si>
   <si>
-    <t>Mês - Numérico</t>
+    <t>Mês - Descritivo</t>
   </si>
   <si>
     <t>Unidade Orçamentária - Código</t>
@@ -38,31 +38,67 @@
     <t>Unidade Orçamentária - Nome</t>
   </si>
   <si>
+    <t>Classificação Receita - Formatado</t>
+  </si>
+  <si>
     <t>Classificação Receita - Descrição</t>
   </si>
   <si>
-    <t>Classificação Receita - Formatado</t>
+    <t>Valor Previsto Inicial</t>
+  </si>
+  <si>
+    <t>Valor Previsto Atualizado</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
   </si>
   <si>
     <t>EMG - ADMINISTRACAO DIRETA</t>
   </si>
   <si>
+    <t>1321.01.0.1.01.000</t>
+  </si>
+  <si>
+    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+  </si>
+  <si>
+    <t>2999.99.0.1.04.000</t>
+  </si>
+  <si>
     <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
   </si>
   <si>
-    <t>2999.99.0.1.04.000</t>
-  </si>
-  <si>
-    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-  </si>
-  <si>
-    <t>1321.01.0.1.01.000</t>
-  </si>
-  <si>
-    <t>Valor Previsto Inicial</t>
-  </si>
-  <si>
-    <t>Valor Previsto Atualizado</t>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>Setembro</t>
   </si>
 </sst>
 </file>
@@ -433,7 +469,9 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.28515625" customWidth="1"/>
+    <col min="3" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="23.28515625" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" customWidth="1"/>
@@ -453,36 +491,36 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>12</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>2024</v>
       </c>
-      <c r="B2" s="3">
-        <v>12</v>
+      <c r="B2" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C2" s="3">
         <v>9999</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" s="5">
         <v>0</v>
@@ -495,20 +533,20 @@
       <c r="A3" s="3">
         <v>2024</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>8</v>
-      </c>
       <c r="F3" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G3" s="5">
         <v>0</v>
@@ -521,20 +559,20 @@
       <c r="A4" s="3">
         <v>2025</v>
       </c>
-      <c r="B4" s="3">
-        <v>1</v>
+      <c r="B4" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C4" s="3">
         <v>9999</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4" s="5">
         <v>0</v>
@@ -547,98 +585,98 @@
       <c r="A5" s="3">
         <v>2025</v>
       </c>
-      <c r="B5" s="3">
-        <v>1</v>
+      <c r="B5" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="C5" s="3">
         <v>9999</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G5" s="5">
-        <v>809526379</v>
+        <v>0</v>
       </c>
       <c r="H5" s="5">
-        <v>809526379</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>2025</v>
       </c>
-      <c r="B6" s="3">
-        <v>2</v>
+      <c r="B6" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="C6" s="3">
         <v>9999</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6" s="5">
         <v>0</v>
       </c>
       <c r="H6" s="5">
-        <v>89000000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>2025</v>
       </c>
-      <c r="B7" s="3">
-        <v>3</v>
+      <c r="B7" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C7" s="3">
         <v>9999</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7" s="5">
         <v>0</v>
       </c>
       <c r="H7" s="5">
-        <v>0</v>
+        <v>89000000</v>
       </c>
     </row>
     <row r="8" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>2025</v>
       </c>
-      <c r="B8" s="3">
-        <v>4</v>
+      <c r="B8" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C8" s="3">
         <v>9999</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G8" s="5">
         <v>0</v>
@@ -651,46 +689,46 @@
       <c r="A9" s="3">
         <v>2025</v>
       </c>
-      <c r="B9" s="3">
-        <v>5</v>
+      <c r="B9" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C9" s="3">
         <v>9999</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G9" s="5">
-        <v>0</v>
+        <v>809526379</v>
       </c>
       <c r="H9" s="5">
-        <v>0</v>
+        <v>809526379</v>
       </c>
     </row>
     <row r="10" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>2025</v>
       </c>
-      <c r="B10" s="3">
-        <v>6</v>
+      <c r="B10" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="C10" s="3">
         <v>9999</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G10" s="5">
         <v>0</v>
@@ -703,20 +741,20 @@
       <c r="A11" s="3">
         <v>2025</v>
       </c>
-      <c r="B11" s="3">
-        <v>6</v>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C11" s="3">
         <v>9999</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G11" s="5">
         <v>0</v>
@@ -729,20 +767,20 @@
       <c r="A12" s="3">
         <v>2025</v>
       </c>
-      <c r="B12" s="3">
-        <v>7</v>
+      <c r="B12" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C12" s="3">
         <v>9999</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G12" s="5">
         <v>0</v>
@@ -755,20 +793,20 @@
       <c r="A13" s="3">
         <v>2025</v>
       </c>
-      <c r="B13" s="3">
-        <v>8</v>
+      <c r="B13" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="C13" s="3">
         <v>9999</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G13" s="5">
         <v>0</v>
@@ -781,20 +819,20 @@
       <c r="A14" s="3">
         <v>2025</v>
       </c>
-      <c r="B14" s="3">
-        <v>9</v>
+      <c r="B14" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C14" s="3">
         <v>9999</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G14" s="5">
         <v>0</v>
@@ -807,20 +845,20 @@
       <c r="A15" s="3">
         <v>2025</v>
       </c>
-      <c r="B15" s="3">
-        <v>10</v>
+      <c r="B15" s="4" t="s">
+        <v>22</v>
       </c>
       <c r="C15" s="3">
         <v>9999</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G15" s="5">
         <v>0</v>
@@ -833,20 +871,20 @@
       <c r="A16" s="3">
         <v>2025</v>
       </c>
-      <c r="B16" s="3">
-        <v>11</v>
+      <c r="B16" s="4" t="s">
+        <v>23</v>
       </c>
       <c r="C16" s="3">
         <v>9999</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G16" s="5">
         <v>0</v>
@@ -859,20 +897,20 @@
       <c r="A17" s="3">
         <v>2025</v>
       </c>
-      <c r="B17" s="3">
-        <v>12</v>
+      <c r="B17" s="4" t="s">
+        <v>24</v>
       </c>
       <c r="C17" s="3">
         <v>9999</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" s="5">
         <v>0</v>
@@ -885,20 +923,20 @@
       <c r="A18" s="3">
         <v>2026</v>
       </c>
-      <c r="B18" s="3">
-        <v>1</v>
+      <c r="B18" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C18" s="3">
         <v>9999</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G18" s="5">
         <v>0</v>
@@ -911,46 +949,46 @@
       <c r="A19" s="3">
         <v>2026</v>
       </c>
-      <c r="B19" s="3">
-        <v>1</v>
+      <c r="B19" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="C19" s="3">
         <v>9999</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="G19" s="5">
-        <v>1141788255</v>
+        <v>0</v>
       </c>
       <c r="H19" s="5">
-        <v>1141788255</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>2026</v>
       </c>
-      <c r="B20" s="3">
-        <v>2</v>
+      <c r="B20" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="C20" s="3">
         <v>9999</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G20" s="5">
         <v>0</v>
@@ -963,20 +1001,20 @@
       <c r="A21" s="3">
         <v>2026</v>
       </c>
-      <c r="B21" s="3">
-        <v>3</v>
+      <c r="B21" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C21" s="3">
         <v>9999</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>10</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G21" s="5">
         <v>0</v>
@@ -989,46 +1027,46 @@
       <c r="A22" s="3">
         <v>2026</v>
       </c>
-      <c r="B22" s="3">
-        <v>4</v>
+      <c r="B22" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="C22" s="3">
         <v>9999</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G22" s="5">
-        <v>0</v>
+        <v>1141788255</v>
       </c>
       <c r="H22" s="5">
-        <v>0</v>
+        <v>1141788255</v>
       </c>
     </row>
     <row r="23" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>2026</v>
       </c>
-      <c r="B23" s="3">
-        <v>4</v>
+      <c r="B23" s="4" t="s">
+        <v>21</v>
       </c>
       <c r="C23" s="3">
         <v>9999</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="G23" s="5">
         <v>0</v>

--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="28">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -99,6 +99,15 @@
   </si>
   <si>
     <t>Setembro</t>
+  </si>
+  <si>
+    <t>Fonte Recurso - Código</t>
+  </si>
+  <si>
+    <t>Fonte Recurso - Descrição</t>
+  </si>
+  <si>
+    <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
   </si>
 </sst>
 </file>
@@ -466,18 +475,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
     <col min="2" max="2" width="15.28515625" customWidth="1"/>
     <col min="3" max="6" width="10.7109375" customWidth="1"/>
-    <col min="7" max="7" width="23.28515625" customWidth="1"/>
-    <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" customWidth="1"/>
+    <col min="7" max="9" width="23.28515625" customWidth="1"/>
+    <col min="10" max="10" width="20" customWidth="1"/>
+    <col min="11" max="11" width="4.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,13 +506,19 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A2" s="3">
         <v>2024</v>
       </c>
@@ -522,14 +537,20 @@
       <c r="F2" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G2" s="5">
-        <v>0</v>
-      </c>
-      <c r="H2" s="5">
+      <c r="G2" s="3">
+        <v>80</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="5">
+        <v>0</v>
+      </c>
+      <c r="J2" s="5">
         <v>4700000</v>
       </c>
     </row>
-    <row r="3" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A3" s="3">
         <v>2024</v>
       </c>
@@ -548,14 +569,20 @@
       <c r="F3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="5">
-        <v>0</v>
-      </c>
-      <c r="H3" s="5">
+      <c r="G3" s="3">
+        <v>80</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0</v>
+      </c>
+      <c r="J3" s="5">
         <v>740335000</v>
       </c>
     </row>
-    <row r="4" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A4" s="3">
         <v>2025</v>
       </c>
@@ -574,14 +601,20 @@
       <c r="F4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G4" s="5">
-        <v>0</v>
-      </c>
-      <c r="H4" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G4" s="3">
+        <v>80</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A5" s="3">
         <v>2025</v>
       </c>
@@ -600,14 +633,20 @@
       <c r="F5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G5" s="5">
-        <v>0</v>
-      </c>
-      <c r="H5" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G5" s="3">
+        <v>80</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A6" s="3">
         <v>2025</v>
       </c>
@@ -626,14 +665,20 @@
       <c r="F6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="5">
-        <v>0</v>
-      </c>
-      <c r="H6" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G6" s="3">
+        <v>80</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A7" s="3">
         <v>2025</v>
       </c>
@@ -652,14 +697,20 @@
       <c r="F7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="5">
-        <v>0</v>
-      </c>
-      <c r="H7" s="5">
+      <c r="G7" s="3">
+        <v>80</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0</v>
+      </c>
+      <c r="J7" s="5">
         <v>89000000</v>
       </c>
     </row>
-    <row r="8" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A8" s="3">
         <v>2025</v>
       </c>
@@ -678,14 +729,20 @@
       <c r="F8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G8" s="5">
-        <v>0</v>
-      </c>
-      <c r="H8" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G8" s="3">
+        <v>80</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I8" s="5">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A9" s="3">
         <v>2025</v>
       </c>
@@ -704,14 +761,20 @@
       <c r="F9" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="3">
+        <v>80</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I9" s="5">
         <v>809526379</v>
       </c>
-      <c r="H9" s="5">
+      <c r="J9" s="5">
         <v>809526379</v>
       </c>
     </row>
-    <row r="10" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A10" s="3">
         <v>2025</v>
       </c>
@@ -730,14 +793,20 @@
       <c r="F10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G10" s="5">
-        <v>0</v>
-      </c>
-      <c r="H10" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G10" s="3">
+        <v>80</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
         <v>2025</v>
       </c>
@@ -756,14 +825,20 @@
       <c r="F11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G11" s="5">
-        <v>0</v>
-      </c>
-      <c r="H11" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G11" s="3">
+        <v>80</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
         <v>2025</v>
       </c>
@@ -782,14 +857,20 @@
       <c r="F12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="5">
-        <v>0</v>
-      </c>
-      <c r="H12" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G12" s="3">
+        <v>80</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A13" s="3">
         <v>2025</v>
       </c>
@@ -808,14 +889,20 @@
       <c r="F13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G13" s="5">
-        <v>0</v>
-      </c>
-      <c r="H13" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G13" s="3">
+        <v>80</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A14" s="3">
         <v>2025</v>
       </c>
@@ -834,14 +921,20 @@
       <c r="F14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G14" s="5">
-        <v>0</v>
-      </c>
-      <c r="H14" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G14" s="3">
+        <v>80</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I14" s="5">
+        <v>0</v>
+      </c>
+      <c r="J14" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A15" s="3">
         <v>2025</v>
       </c>
@@ -860,14 +953,20 @@
       <c r="F15" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G15" s="5">
-        <v>0</v>
-      </c>
-      <c r="H15" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G15" s="3">
+        <v>80</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I15" s="5">
+        <v>0</v>
+      </c>
+      <c r="J15" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A16" s="3">
         <v>2025</v>
       </c>
@@ -886,14 +985,20 @@
       <c r="F16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G16" s="5">
-        <v>0</v>
-      </c>
-      <c r="H16" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G16" s="3">
+        <v>80</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0</v>
+      </c>
+      <c r="J16" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A17" s="3">
         <v>2025</v>
       </c>
@@ -912,14 +1017,20 @@
       <c r="F17" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G17" s="5">
-        <v>0</v>
-      </c>
-      <c r="H17" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G17" s="3">
+        <v>80</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I17" s="5">
+        <v>0</v>
+      </c>
+      <c r="J17" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A18" s="3">
         <v>2026</v>
       </c>
@@ -938,14 +1049,20 @@
       <c r="F18" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G18" s="5">
-        <v>0</v>
-      </c>
-      <c r="H18" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G18" s="3">
+        <v>80</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I18" s="5">
+        <v>0</v>
+      </c>
+      <c r="J18" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A19" s="3">
         <v>2026</v>
       </c>
@@ -964,14 +1081,20 @@
       <c r="F19" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="5">
-        <v>0</v>
-      </c>
-      <c r="H19" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G19" s="3">
+        <v>80</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+      <c r="J19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A20" s="3">
         <v>2026</v>
       </c>
@@ -990,14 +1113,20 @@
       <c r="F20" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G20" s="5">
-        <v>0</v>
-      </c>
-      <c r="H20" s="5">
+      <c r="G20" s="3">
+        <v>80</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0</v>
+      </c>
+      <c r="J20" s="5">
         <v>960000000</v>
       </c>
     </row>
-    <row r="21" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A21" s="3">
         <v>2026</v>
       </c>
@@ -1016,14 +1145,20 @@
       <c r="F21" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G21" s="5">
-        <v>0</v>
-      </c>
-      <c r="H21" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="G21" s="3">
+        <v>80</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="J21" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A22" s="3">
         <v>2026</v>
       </c>
@@ -1042,14 +1177,20 @@
       <c r="F22" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="3">
+        <v>80</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I22" s="5">
         <v>1141788255</v>
       </c>
-      <c r="H22" s="5">
+      <c r="J22" s="5">
         <v>1141788255</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
       <c r="A23" s="3">
         <v>2026</v>
       </c>
@@ -1068,14 +1209,20 @@
       <c r="F23" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="G23" s="5">
-        <v>0</v>
-      </c>
-      <c r="H23" s="5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+      <c r="G23" s="3">
+        <v>80</v>
+      </c>
+      <c r="H23" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="I23" s="5">
+        <v>0</v>
+      </c>
+      <c r="J23" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Documents\transparencia-mg\portal_mariana\upload\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\m11483500\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="28">
   <si>
     <t>Ano de Exercício</t>
   </si>
@@ -38,76 +38,76 @@
     <t>Unidade Orçamentária - Nome</t>
   </si>
   <si>
+    <t>Classificação Receita - Descrição</t>
+  </si>
+  <si>
     <t>Classificação Receita - Formatado</t>
   </si>
   <si>
-    <t>Classificação Receita - Descrição</t>
+    <t>Fonte Recurso - Código</t>
+  </si>
+  <si>
+    <t>Fonte Recurso - Descrição</t>
+  </si>
+  <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>EMG - ADMINISTRACAO DIRETA</t>
+  </si>
+  <si>
+    <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
+  </si>
+  <si>
+    <t>2999.99.0.1.04.000</t>
+  </si>
+  <si>
+    <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+  </si>
+  <si>
+    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+  </si>
+  <si>
+    <t>1321.01.0.1.01.000</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>Setembro</t>
   </si>
   <si>
     <t>Valor Previsto Inicial</t>
   </si>
   <si>
     <t>Valor Previsto Atualizado</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>EMG - ADMINISTRACAO DIRETA</t>
-  </si>
-  <si>
-    <t>1321.01.0.1.01.000</t>
-  </si>
-  <si>
-    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-  </si>
-  <si>
-    <t>2999.99.0.1.04.000</t>
-  </si>
-  <si>
-    <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>Fevereiro</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>Junho</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>Novembro</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>Fonte Recurso - Código</t>
-  </si>
-  <si>
-    <t>Fonte Recurso - Descrição</t>
-  </si>
-  <si>
-    <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
   </si>
 </sst>
 </file>
@@ -475,7 +475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.7109375" customWidth="1"/>
@@ -500,22 +500,22 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
       <c r="G1" s="1" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="I1" s="1" t="s">
-        <v>6</v>
-      </c>
       <c r="J1" s="1" t="s">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -532,16 +532,16 @@
         <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G2" s="3">
         <v>80</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I2" s="5">
         <v>0</v>
@@ -564,16 +564,16 @@
         <v>9</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G3" s="3">
         <v>80</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
@@ -587,7 +587,7 @@
         <v>2025</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3">
         <v>9999</v>
@@ -596,16 +596,16 @@
         <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G4" s="3">
         <v>80</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
@@ -619,7 +619,7 @@
         <v>2025</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3">
         <v>9999</v>
@@ -628,16 +628,16 @@
         <v>9</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3">
         <v>80</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
@@ -660,16 +660,16 @@
         <v>9</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G6" s="3">
         <v>80</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
@@ -683,7 +683,7 @@
         <v>2025</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3">
         <v>9999</v>
@@ -692,16 +692,16 @@
         <v>9</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G7" s="3">
         <v>80</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
@@ -715,7 +715,7 @@
         <v>2025</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3">
         <v>9999</v>
@@ -724,16 +724,16 @@
         <v>9</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G8" s="3">
         <v>80</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I8" s="5">
         <v>0</v>
@@ -747,7 +747,7 @@
         <v>2025</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
         <v>9999</v>
@@ -756,16 +756,16 @@
         <v>9</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G9" s="3">
         <v>80</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I9" s="5">
         <v>809526379</v>
@@ -779,7 +779,7 @@
         <v>2025</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3">
         <v>9999</v>
@@ -788,16 +788,16 @@
         <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G10" s="3">
         <v>80</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
@@ -811,7 +811,7 @@
         <v>2025</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3">
         <v>9999</v>
@@ -820,16 +820,16 @@
         <v>9</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G11" s="3">
         <v>80</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I11" s="5">
         <v>0</v>
@@ -843,7 +843,7 @@
         <v>2025</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3">
         <v>9999</v>
@@ -852,16 +852,16 @@
         <v>9</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G12" s="3">
         <v>80</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
@@ -875,7 +875,7 @@
         <v>2025</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3">
         <v>9999</v>
@@ -884,16 +884,16 @@
         <v>9</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G13" s="3">
         <v>80</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I13" s="5">
         <v>0</v>
@@ -907,7 +907,7 @@
         <v>2025</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3">
         <v>9999</v>
@@ -916,16 +916,16 @@
         <v>9</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G14" s="3">
         <v>80</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I14" s="5">
         <v>0</v>
@@ -939,7 +939,7 @@
         <v>2025</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3">
         <v>9999</v>
@@ -948,16 +948,16 @@
         <v>9</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G15" s="3">
         <v>80</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I15" s="5">
         <v>0</v>
@@ -971,7 +971,7 @@
         <v>2025</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3">
         <v>9999</v>
@@ -980,16 +980,16 @@
         <v>9</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G16" s="3">
         <v>80</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
@@ -1003,7 +1003,7 @@
         <v>2025</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3">
         <v>9999</v>
@@ -1012,16 +1012,16 @@
         <v>9</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G17" s="3">
         <v>80</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I17" s="5">
         <v>0</v>
@@ -1035,7 +1035,7 @@
         <v>2026</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" s="3">
         <v>9999</v>
@@ -1044,16 +1044,16 @@
         <v>9</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G18" s="3">
         <v>80</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I18" s="5">
         <v>0</v>
@@ -1067,7 +1067,7 @@
         <v>2026</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3">
         <v>9999</v>
@@ -1076,16 +1076,16 @@
         <v>9</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G19" s="3">
         <v>80</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I19" s="5">
         <v>0</v>
@@ -1099,7 +1099,7 @@
         <v>2026</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3">
         <v>9999</v>
@@ -1108,16 +1108,16 @@
         <v>9</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G20" s="3">
         <v>80</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>2026</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C21" s="3">
         <v>9999</v>
@@ -1140,16 +1140,16 @@
         <v>9</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G21" s="3">
         <v>80</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I21" s="5">
         <v>0</v>
@@ -1163,7 +1163,7 @@
         <v>2026</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3">
         <v>9999</v>
@@ -1172,16 +1172,16 @@
         <v>9</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G22" s="3">
         <v>80</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I22" s="5">
         <v>1141788255</v>
@@ -1204,16 +1204,16 @@
         <v>9</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G23" s="3">
         <v>80</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
@@ -1222,7 +1222,39 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
+    <row r="24" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
+      <c r="A24" s="3">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G24" s="3">
+        <v>80</v>
+      </c>
+      <c r="H24" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="I24" s="5">
+        <v>0</v>
+      </c>
+      <c r="J24" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2"/>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="11130"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -38,39 +38,45 @@
     <t>Unidade Orçamentária - Nome</t>
   </si>
   <si>
+    <t>Classificação Receita - Formatado</t>
+  </si>
+  <si>
     <t>Classificação Receita - Descrição</t>
   </si>
   <si>
-    <t>Classificação Receita - Formatado</t>
-  </si>
-  <si>
     <t>Fonte Recurso - Código</t>
   </si>
   <si>
     <t>Fonte Recurso - Descrição</t>
   </si>
   <si>
+    <t>Valor Previsto Inicial</t>
+  </si>
+  <si>
+    <t>Valor Previsto Atualizado</t>
+  </si>
+  <si>
     <t>Dezembro</t>
   </si>
   <si>
     <t>EMG - ADMINISTRACAO DIRETA</t>
   </si>
   <si>
+    <t>1321.01.0.1.01.000</t>
+  </si>
+  <si>
+    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+  </si>
+  <si>
+    <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+  </si>
+  <si>
+    <t>2999.99.0.1.04.000</t>
+  </si>
+  <si>
     <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
   </si>
   <si>
-    <t>2999.99.0.1.04.000</t>
-  </si>
-  <si>
-    <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-  </si>
-  <si>
-    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-  </si>
-  <si>
-    <t>1321.01.0.1.01.000</t>
-  </si>
-  <si>
     <t>Abril</t>
   </si>
   <si>
@@ -102,12 +108,6 @@
   </si>
   <si>
     <t>Setembro</t>
-  </si>
-  <si>
-    <t>Valor Previsto Inicial</t>
-  </si>
-  <si>
-    <t>Valor Previsto Atualizado</t>
   </si>
 </sst>
 </file>
@@ -500,10 +500,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -512,10 +512,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -523,16 +523,16 @@
         <v>2024</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="3">
         <v>9999</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>13</v>
@@ -541,7 +541,7 @@
         <v>80</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I2" s="5">
         <v>0</v>
@@ -555,25 +555,25 @@
         <v>2024</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C3" s="3">
         <v>9999</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G3" s="3">
         <v>80</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
@@ -587,16 +587,16 @@
         <v>2025</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C4" s="3">
         <v>9999</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>13</v>
@@ -605,7 +605,7 @@
         <v>80</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
@@ -619,16 +619,16 @@
         <v>2025</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C5" s="3">
         <v>9999</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>13</v>
@@ -637,7 +637,7 @@
         <v>80</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
@@ -651,16 +651,16 @@
         <v>2025</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C6" s="3">
         <v>9999</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>13</v>
@@ -669,7 +669,7 @@
         <v>80</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
@@ -683,16 +683,16 @@
         <v>2025</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C7" s="3">
         <v>9999</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>13</v>
@@ -701,7 +701,7 @@
         <v>80</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
@@ -715,16 +715,16 @@
         <v>2025</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3">
         <v>9999</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>13</v>
@@ -733,7 +733,7 @@
         <v>80</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I8" s="5">
         <v>0</v>
@@ -747,25 +747,25 @@
         <v>2025</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" s="3">
         <v>9999</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G9" s="3">
         <v>80</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I9" s="5">
         <v>809526379</v>
@@ -779,16 +779,16 @@
         <v>2025</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C10" s="3">
         <v>9999</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>13</v>
@@ -797,7 +797,7 @@
         <v>80</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
@@ -811,16 +811,16 @@
         <v>2025</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C11" s="3">
         <v>9999</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>13</v>
@@ -829,7 +829,7 @@
         <v>80</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I11" s="5">
         <v>0</v>
@@ -843,25 +843,25 @@
         <v>2025</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C12" s="3">
         <v>9999</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G12" s="3">
         <v>80</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
@@ -875,16 +875,16 @@
         <v>2025</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C13" s="3">
         <v>9999</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>13</v>
@@ -893,7 +893,7 @@
         <v>80</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I13" s="5">
         <v>0</v>
@@ -907,16 +907,16 @@
         <v>2025</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C14" s="3">
         <v>9999</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>13</v>
@@ -925,7 +925,7 @@
         <v>80</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I14" s="5">
         <v>0</v>
@@ -939,16 +939,16 @@
         <v>2025</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C15" s="3">
         <v>9999</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>13</v>
@@ -957,7 +957,7 @@
         <v>80</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I15" s="5">
         <v>0</v>
@@ -971,16 +971,16 @@
         <v>2025</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C16" s="3">
         <v>9999</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>13</v>
@@ -989,7 +989,7 @@
         <v>80</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
@@ -1003,16 +1003,16 @@
         <v>2025</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C17" s="3">
         <v>9999</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>13</v>
@@ -1021,7 +1021,7 @@
         <v>80</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I17" s="5">
         <v>0</v>
@@ -1035,16 +1035,16 @@
         <v>2026</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C18" s="3">
         <v>9999</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>13</v>
@@ -1053,7 +1053,7 @@
         <v>80</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I18" s="5">
         <v>0</v>
@@ -1067,25 +1067,25 @@
         <v>2026</v>
       </c>
       <c r="B19" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C19" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="F19" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G19" s="3">
         <v>80</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I19" s="5">
         <v>0</v>
@@ -1099,16 +1099,16 @@
         <v>2026</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C20" s="3">
         <v>9999</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>13</v>
@@ -1117,7 +1117,7 @@
         <v>80</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
@@ -1131,16 +1131,16 @@
         <v>2026</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C21" s="3">
         <v>9999</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>13</v>
@@ -1149,7 +1149,7 @@
         <v>80</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I21" s="5">
         <v>0</v>
@@ -1163,25 +1163,25 @@
         <v>2026</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C22" s="3">
         <v>9999</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="G22" s="3">
         <v>80</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I22" s="5">
         <v>1141788255</v>
@@ -1195,16 +1195,16 @@
         <v>2026</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C23" s="3">
         <v>9999</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>13</v>
@@ -1213,7 +1213,7 @@
         <v>80</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
@@ -1227,16 +1227,16 @@
         <v>2026</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C24" s="3">
         <v>9999</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>13</v>
@@ -1245,7 +1245,7 @@
         <v>80</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I24" s="5">
         <v>0</v>

--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8430"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21600" windowHeight="8400"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
@@ -38,76 +38,76 @@
     <t>Unidade Orçamentária - Nome</t>
   </si>
   <si>
+    <t>Classificação Receita - Descrição</t>
+  </si>
+  <si>
     <t>Classificação Receita - Formatado</t>
   </si>
   <si>
-    <t>Classificação Receita - Descrição</t>
-  </si>
-  <si>
     <t>Fonte Recurso - Código</t>
   </si>
   <si>
     <t>Fonte Recurso - Descrição</t>
   </si>
   <si>
+    <t>Dezembro</t>
+  </si>
+  <si>
+    <t>EMG - ADMINISTRACAO DIRETA</t>
+  </si>
+  <si>
+    <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
+  </si>
+  <si>
+    <t>2999.99.0.1.04.000</t>
+  </si>
+  <si>
+    <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+  </si>
+  <si>
+    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+  </si>
+  <si>
+    <t>1321.01.0.1.01.000</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>Agosto</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>Janeiro</t>
+  </si>
+  <si>
+    <t>Julho</t>
+  </si>
+  <si>
+    <t>Junho</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>Novembro</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
     <t>Valor Previsto Inicial</t>
   </si>
   <si>
     <t>Valor Previsto Atualizado</t>
-  </si>
-  <si>
-    <t>Dezembro</t>
-  </si>
-  <si>
-    <t>EMG - ADMINISTRACAO DIRETA</t>
-  </si>
-  <si>
-    <t>1321.01.0.1.01.000</t>
-  </si>
-  <si>
-    <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-  </si>
-  <si>
-    <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-  </si>
-  <si>
-    <t>2999.99.0.1.04.000</t>
-  </si>
-  <si>
-    <t>DEMAIS REC. CAPITAL - PRINC. - ROMPIMENTO DA BARRAGEM DE FUNDAO EM MARIANA - ACORDO JUDICIAL DE REPARACAO INTEGRAL E DEFINITIVA</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>Agosto</t>
-  </si>
-  <si>
-    <t>Fevereiro</t>
-  </si>
-  <si>
-    <t>Janeiro</t>
-  </si>
-  <si>
-    <t>Julho</t>
-  </si>
-  <si>
-    <t>Junho</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>Novembro</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>Setembro</t>
   </si>
 </sst>
 </file>
@@ -500,10 +500,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
@@ -512,10 +512,10 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>9</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:10" s="2" customFormat="1" ht="12" x14ac:dyDescent="0.2">
@@ -523,16 +523,16 @@
         <v>2024</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3">
         <v>9999</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>13</v>
@@ -541,7 +541,7 @@
         <v>80</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I2" s="5">
         <v>0</v>
@@ -555,25 +555,25 @@
         <v>2024</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="3">
+        <v>9999</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3">
-        <v>9999</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>16</v>
-      </c>
       <c r="G3" s="3">
         <v>80</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I3" s="5">
         <v>0</v>
@@ -587,16 +587,16 @@
         <v>2025</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3">
         <v>9999</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4" t="s">
         <v>13</v>
@@ -605,7 +605,7 @@
         <v>80</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I4" s="5">
         <v>0</v>
@@ -619,16 +619,16 @@
         <v>2025</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C5" s="3">
         <v>9999</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>13</v>
@@ -637,7 +637,7 @@
         <v>80</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I5" s="5">
         <v>0</v>
@@ -651,16 +651,16 @@
         <v>2025</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C6" s="3">
         <v>9999</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F6" s="4" t="s">
         <v>13</v>
@@ -669,7 +669,7 @@
         <v>80</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I6" s="5">
         <v>0</v>
@@ -683,16 +683,16 @@
         <v>2025</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3">
         <v>9999</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F7" s="4" t="s">
         <v>13</v>
@@ -701,7 +701,7 @@
         <v>80</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I7" s="5">
         <v>0</v>
@@ -715,16 +715,16 @@
         <v>2025</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" s="3">
         <v>9999</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>13</v>
@@ -733,7 +733,7 @@
         <v>80</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I8" s="5">
         <v>0</v>
@@ -747,25 +747,25 @@
         <v>2025</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C9" s="3">
         <v>9999</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="F9" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G9" s="3">
         <v>80</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I9" s="5">
         <v>809526379</v>
@@ -779,16 +779,16 @@
         <v>2025</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" s="3">
         <v>9999</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F10" s="4" t="s">
         <v>13</v>
@@ -797,7 +797,7 @@
         <v>80</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I10" s="5">
         <v>0</v>
@@ -811,16 +811,16 @@
         <v>2025</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" s="3">
         <v>9999</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>13</v>
@@ -829,7 +829,7 @@
         <v>80</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I11" s="5">
         <v>0</v>
@@ -843,25 +843,25 @@
         <v>2025</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="3">
         <v>9999</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="F12" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G12" s="3">
         <v>80</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I12" s="5">
         <v>0</v>
@@ -875,16 +875,16 @@
         <v>2025</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C13" s="3">
         <v>9999</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>13</v>
@@ -893,7 +893,7 @@
         <v>80</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I13" s="5">
         <v>0</v>
@@ -907,16 +907,16 @@
         <v>2025</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3">
         <v>9999</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F14" s="4" t="s">
         <v>13</v>
@@ -925,7 +925,7 @@
         <v>80</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I14" s="5">
         <v>0</v>
@@ -939,16 +939,16 @@
         <v>2025</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3">
         <v>9999</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>13</v>
@@ -957,7 +957,7 @@
         <v>80</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I15" s="5">
         <v>0</v>
@@ -971,16 +971,16 @@
         <v>2025</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3">
         <v>9999</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>13</v>
@@ -989,7 +989,7 @@
         <v>80</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I16" s="5">
         <v>0</v>
@@ -1003,16 +1003,16 @@
         <v>2025</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C17" s="3">
         <v>9999</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F17" s="4" t="s">
         <v>13</v>
@@ -1021,7 +1021,7 @@
         <v>80</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I17" s="5">
         <v>0</v>
@@ -1035,16 +1035,16 @@
         <v>2026</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C18" s="3">
         <v>9999</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F18" s="4" t="s">
         <v>13</v>
@@ -1053,7 +1053,7 @@
         <v>80</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I18" s="5">
         <v>0</v>
@@ -1067,25 +1067,25 @@
         <v>2026</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C19" s="3">
         <v>9999</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E19" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="F19" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G19" s="3">
         <v>80</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I19" s="5">
         <v>0</v>
@@ -1099,16 +1099,16 @@
         <v>2026</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C20" s="3">
         <v>9999</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F20" s="4" t="s">
         <v>13</v>
@@ -1117,7 +1117,7 @@
         <v>80</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I20" s="5">
         <v>0</v>
@@ -1131,16 +1131,16 @@
         <v>2026</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C21" s="3">
         <v>9999</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>13</v>
@@ -1149,7 +1149,7 @@
         <v>80</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I21" s="5">
         <v>0</v>
@@ -1163,25 +1163,25 @@
         <v>2026</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C22" s="3">
         <v>9999</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E22" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>15</v>
-      </c>
       <c r="F22" s="4" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G22" s="3">
         <v>80</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I22" s="5">
         <v>1141788255</v>
@@ -1195,16 +1195,16 @@
         <v>2026</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C23" s="3">
         <v>9999</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F23" s="4" t="s">
         <v>13</v>
@@ -1213,7 +1213,7 @@
         <v>80</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I23" s="5">
         <v>0</v>
@@ -1227,16 +1227,16 @@
         <v>2026</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="C24" s="3">
         <v>9999</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F24" s="4" t="s">
         <v>13</v>
@@ -1245,7 +1245,7 @@
         <v>80</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="I24" s="5">
         <v>0</v>

--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,6 +479,11 @@
           <t>Valor Previsto Atualizado</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Valor Efetivado Ajustado</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -521,6 +526,9 @@
       <c r="J2" t="n">
         <v>4700000</v>
       </c>
+      <c r="K2" t="n">
+        <v>4600135.94</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -563,6 +571,9 @@
       <c r="J3" t="n">
         <v>740335000</v>
       </c>
+      <c r="K3" t="n">
+        <v>740335914.3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -605,6 +616,9 @@
       <c r="J4" t="n">
         <v>0</v>
       </c>
+      <c r="K4" t="n">
+        <v>7970149.65</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -647,6 +661,9 @@
       <c r="J5" t="n">
         <v>0</v>
       </c>
+      <c r="K5" t="n">
+        <v>20665598.17</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -689,6 +706,9 @@
       <c r="J6" t="n">
         <v>0</v>
       </c>
+      <c r="K6" t="n">
+        <v>21574633.64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -731,6 +751,9 @@
       <c r="J7" t="n">
         <v>89000000</v>
       </c>
+      <c r="K7" t="n">
+        <v>1931832.88</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -773,6 +796,9 @@
       <c r="J8" t="n">
         <v>0</v>
       </c>
+      <c r="K8" t="n">
+        <v>7398834.46</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -815,6 +841,9 @@
       <c r="J9" t="n">
         <v>809526379</v>
       </c>
+      <c r="K9" t="n">
+        <v>275043.58</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -857,6 +886,9 @@
       <c r="J10" t="n">
         <v>0</v>
       </c>
+      <c r="K10" t="n">
+        <v>22427853.45</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -899,6 +931,9 @@
       <c r="J11" t="n">
         <v>0</v>
       </c>
+      <c r="K11" t="n">
+        <v>16983866.92</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -941,6 +976,9 @@
       <c r="J12" t="n">
         <v>0</v>
       </c>
+      <c r="K12" t="n">
+        <v>1001443461.88</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -983,6 +1021,9 @@
       <c r="J13" t="n">
         <v>0</v>
       </c>
+      <c r="K13" t="n">
+        <v>8609495.35</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1025,6 +1066,9 @@
       <c r="J14" t="n">
         <v>0</v>
       </c>
+      <c r="K14" t="n">
+        <v>12559500.71</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1067,6 +1111,9 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
+      <c r="K15" t="n">
+        <v>18924889.14</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1109,6 +1156,9 @@
       <c r="J16" t="n">
         <v>0</v>
       </c>
+      <c r="K16" t="n">
+        <v>11116248.04</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1151,6 +1201,9 @@
       <c r="J17" t="n">
         <v>0</v>
       </c>
+      <c r="K17" t="n">
+        <v>33649951.89</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1193,6 +1246,9 @@
       <c r="J18" t="n">
         <v>0</v>
       </c>
+      <c r="K18" t="n">
+        <v>18942112.58</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1235,6 +1291,9 @@
       <c r="J19" t="n">
         <v>0</v>
       </c>
+      <c r="K19" t="n">
+        <v>1235142134.67</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1277,6 +1336,9 @@
       <c r="J20" t="n">
         <v>960000000</v>
       </c>
+      <c r="K20" t="n">
+        <v>17183256.57</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1319,6 +1381,9 @@
       <c r="J21" t="n">
         <v>0</v>
       </c>
+      <c r="K21" t="n">
+        <v>20377508.26</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1361,6 +1426,9 @@
       <c r="J22" t="n">
         <v>1141788255</v>
       </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1368,7 +1436,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1402,6 +1470,9 @@
       </c>
       <c r="J23" t="n">
         <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1156960.11</v>
       </c>
     </row>
     <row r="24">
@@ -1410,40 +1481,88 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>80</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>0</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>Março</t>
         </is>
       </c>
-      <c r="C24" t="n">
-        <v>9999</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>EMG - ADMINISTRACAO DIRETA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>1321.01.0.1.01.000</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>80</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
+      <c r="C25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>80</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>20910819.96</v>
       </c>
     </row>
   </sheetData>

--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1517,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>31794430.57</v>
       </c>
     </row>
     <row r="25">

--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-1156960.11</v>
+        <v>-1239043.47</v>
       </c>
     </row>
     <row r="24">

--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1436,7 +1436,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Junho</t>
+          <t>Julho</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>-1239043.47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Maio</t>
+          <t>Junho</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1517,7 +1517,7 @@
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>31794430.57</v>
+        <v>32196417.6</v>
       </c>
     </row>
     <row r="25">
@@ -1526,42 +1526,87 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
+          <t>Maio</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>80</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>31794430.57</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2026</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>Março</t>
         </is>
       </c>
-      <c r="C25" t="n">
-        <v>9999</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>EMG - ADMINISTRACAO DIRETA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>1321.01.0.1.01.000</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>80</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
+      <c r="C26" t="n">
+        <v>9999</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EMG - ADMINISTRACAO DIRETA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1321.01.0.1.01.000</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>REMUNERACAO DEPOSITOS BANCARIOS - PRINC.</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>80</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>RECURSOS DO ACORDO DE REPACTUACAO DO RIO DOCE</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" t="n">
         <v>20910819.96</v>
       </c>
     </row>

--- a/upload/receita.xlsx
+++ b/upload/receita.xlsx
@@ -1472,7 +1472,7 @@
         <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>-198924.52</v>
       </c>
     </row>
     <row r="24">
